--- a/www/download/COUNTRY.AUT.rpO1.xlsx
+++ b/www/download/COUNTRY.AUT.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Áustria</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.731818001159724</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>0.769047362910261</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.885708209560329</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.89831921167159</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0.938262383745538</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>1.08271976620737</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>1.11656987330822</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>1.05752964594517</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>0.884017009908191</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.803923182414509</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>0.803793923570613</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>0.796432004858313</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>0.729660722254592</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902074833737</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.71694869546993</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.717</t>
+          <t>2.1987434316222</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.746</t>
+          <t>2.11280664285165</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3.773</t>
+          <t>2.04531959289115</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.813</t>
+          <t>2.01559873788886</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3.881</t>
+          <t>2.12278212505547</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.931</t>
+          <t>2.07400323501582</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.959</t>
+          <t>2.00558724431268</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.959</t>
+          <t>2.05238599378704</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3.971</t>
+          <t>2.25912554669052</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3.986</t>
+          <t>2.04412942726551</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.031</t>
+          <t>2.08052214122754</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>1.97989149024249</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.161</t>
+          <t>1.87363862157066</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>1.74998356712492</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.213</t>
+          <t>1.73237775197119</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.126</t>
+          <t>3.52862229892583</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.123</t>
+          <t>3.41461609458868</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.151</t>
+          <t>3.30721195978158</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.184</t>
+          <t>3.2834689856988</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.239</t>
+          <t>3.45378830504235</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.278</t>
+          <t>3.37637256324731</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.26779653536426</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.293</t>
+          <t>3.34177637015696</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>3.302</t>
+          <t>3.62830317439473</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3.315</t>
+          <t>3.42816434010312</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3.353</t>
+          <t>3.43694384617567</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3.408</t>
+          <t>3.34657433840743</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>3.22037303926455</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>3.569</t>
+          <t>3.13277660464457</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>3.543</t>
+          <t>3.06612725669408</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6149.242</t>
+          <t>5.24378722941684</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6212.278</t>
+          <t>5.08012188124394</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6288.025</t>
+          <t>4.91036392966687</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6361.278</t>
+          <t>4.97678229456568</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6424.814</t>
+          <t>5.21540781696164</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6518.098</t>
+          <t>5.08689869775253</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6559.398</t>
+          <t>4.96494851241462</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6542.049</t>
+          <t>5.04410939760999</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6583.091</t>
+          <t>3.8367754838327</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6630.014</t>
+          <t>5.0636868681499</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6658.907</t>
+          <t>5.09117307214755</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>6717.025</t>
+          <t>5.02143297128475</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>6788.639</t>
+          <t>5.25339301566475</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6968.04</t>
+          <t>5.40643793360468</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>6613.166</t>
+          <t>5.33102331480262</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4827.845</t>
+          <t>11358921467812.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4833.915</t>
+          <t>9902551878467.27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4916.552</t>
+          <t>9193773489484.58</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4991.233</t>
+          <t>10452005637462.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5053.095</t>
+          <t>11068492109541.9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5121.332</t>
+          <t>11425357592051.1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5161.275</t>
+          <t>12247395010550.2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5133.78</t>
+          <t>12547991834073.8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5169.977</t>
+          <t>14639830549625.4</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5204.784</t>
+          <t>13759707891477.1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5217.574</t>
+          <t>12699533082189.2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5277.349</t>
+          <t>11737173648992.9</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>5371.388</t>
+          <t>10082988304586.6</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>5486.016</t>
+          <t>7956110610441.12</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>5327.349</t>
+          <t>7197990963003.93</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>2296484361031.34</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.86</t>
+          <t>1982474391955.54</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>1797016581322.2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>2038627792776.02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2151444868146.95</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>20.27</t>
+          <t>2182296578503.56</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>2303111156660.22</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>2380452389327.19</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>2760857877896.88</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>24.92</t>
+          <t>2558018672165.52</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>2358144651946.93</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>2132619442514.89</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>1831757687206.4</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>1553846177837.44</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>1434100343792.44</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>1118584306.55855</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>68.05</t>
+          <t>995415067.346593</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>68.62</t>
+          <t>1028719592.67296</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>68.52</t>
+          <t>1155690537.80343</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>65.65</t>
+          <t>1237322495.01166</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>65.53</t>
+          <t>1383042363.85428</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>1451524841.64918</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>66.11</t>
+          <t>1374479921.8131</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>63.58</t>
+          <t>1318273601.92961</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>1070373935.64808</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>64.33</t>
+          <t>948249917.283216</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>796083566.865969</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>63.94</t>
+          <t>579228833.738631</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>65.14</t>
+          <t>394905765.622486</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>64.9</t>
+          <t>408980396.237578</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15.99</t>
+          <t>303851.024336563</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15.09</t>
+          <t>296596.950262435</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14.59</t>
+          <t>268428.84810929</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>278759.57547843</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>277575.448418346</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>252897.739542149</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>252063.961202068</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13.15</t>
+          <t>271895.443151274</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>16.83</t>
+          <t>331410.290230152</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>11.94</t>
+          <t>374610.505804585</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11.65</t>
+          <t>383172.384781259</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>12.17</t>
+          <t>402331.717845237</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>12.03</t>
+          <t>461585.886507078</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>522119.654423703</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>505717.531891943</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>510659.426153529</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>500036.635338645</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>454493.789429903</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>468905.121528184</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>462867.764255642</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>13.97</t>
+          <t>421284.028367891</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>14.03</t>
+          <t>427022.585354324</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.42</t>
+          <t>457421.386659118</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>14.32</t>
+          <t>560744.17530408</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>633449.522351477</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>654438.247042289</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>16.5</t>
+          <t>701606.176583241</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>803783.410866827</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>845001.342585954</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>795913.16514963</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>66.74</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>67.97</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>66.21</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>66.86</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>67.04</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.46</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>66.46</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>66.07</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>66.52</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>59901.0426002679</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>58955.8214361285</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>52871.3513691017</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20.35</t>
+          <t>53578.2391026702</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>51904.1190995353</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>46592.9164193703</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>46102.1829849342</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>48568.3359570759</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>58379.2194962324</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>65964.509659506</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>67187.6205118588</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>17.43</t>
+          <t>69340.3607585595</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>18.12</t>
+          <t>76483.747158246</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>17.37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>15.93</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.731818001159724</t>
+          <t>734599.021369679</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.769047362910261</t>
+          <t>634881.019344038</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.885708209560329</t>
+          <t>570382.588072735</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.89831921167159</t>
+          <t>640172.219484454</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262383745538</t>
+          <t>664238.996365794</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271976620737</t>
+          <t>665813.180425665</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987330822</t>
+          <t>697871.02240601</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964594517</t>
+          <t>722981.61373671</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017009908191</t>
+          <t>836154.086174304</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923182414509</t>
+          <t>771658.05485837</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793923570613</t>
+          <t>703363.605327736</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796432004858313</t>
+          <t>625852.723903298</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660722254592</t>
+          <t>526439.612580698</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902074833737</t>
+          <t>435338.951602674</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.71694869546993</t>
+          <t>404766.638665899</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>-214806878223.765</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>-184700560629.067</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>-176906157510.577</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>-194719461382.671</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-172070961350.99</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>-142754737282.47</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>-88371840888.1477</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>-42273641003.1531</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>-131235291243.638</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>-77765903458.1372</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>1171027330.85324</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>65712136035.8577</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>53717558224.8593</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>96445602282.1049</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>-16042618784.1017</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-245360148313.512</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>-192938362078.354</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>-197097142128.492</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>-251163788644.019</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-284829507075.723</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>-278884211749.695</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>-270367699267.242</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>-231290277402.653</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>-332090661210.492</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>-282421873636.7</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>-249855053645.117</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>-224172689398.678</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>-196031145703.389</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>-124935350162.095</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>-193784674720.484</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.858</t>
+          <t>30553270089.7468</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>8237801449.28749</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>20190984617.9154</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>56444327261.3479</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>112758545724.733</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>136129474467.225</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>181995858379.094</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>189016636399.5</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>200855369966.854</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>204655970178.562</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>251026080975.97</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>1.071</t>
+          <t>289884825434.536</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.216</t>
+          <t>249748703928.249</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>221380952444.2</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>177742055936.382</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>3292823.68693557</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>2761404.11566224</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>2416869.82026052</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>2697985.47510425</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>2887533.15502645</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>2837666.56710295</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>2894238.07935077</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>3040956.06465583</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.451</t>
+          <t>3615571.99661543</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>3239976.66177303</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>2973239.67587855</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>2592632.86641035</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>2132343.23188813</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.799</t>
+          <t>1719482.194726</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>1565083.42803348</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>3280482.81930505</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>2872100.43880125</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>2646992.1462226</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>3019527.70543234</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>3199099.52776089</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>3284749.70536834</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>3459504.2322079</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>3593097.64128587</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>4186032.74187372</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>3939248.78716896</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>3628162.09390896</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>3258193.8315361</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>2755334.57570258</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>2276753.71453304</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>2151607.6305248</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>219.87</t>
+          <t>70221.1915103936</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>211.28</t>
+          <t>71629.4205159264</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>204.53</t>
+          <t>71205.5404294847</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>201.56</t>
+          <t>77143.1228463394</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>212.28</t>
+          <t>78761.5458660388</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>207.4</t>
+          <t>78442.822771672</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>200.56</t>
+          <t>82279.5699330537</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>205.24</t>
+          <t>90534.7975304621</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>225.91</t>
+          <t>109342.604936076</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>204.41</t>
+          <t>132051.931142555</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>208.05</t>
+          <t>144305.812951195</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>197.99</t>
+          <t>162637.198567264</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>187.36</t>
+          <t>194688.095693501</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>218578.155408561</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>173.24</t>
+          <t>168010.107892263</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>352.86</t>
+          <t>2391276309039.32</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>341.46</t>
+          <t>2176866397705.78</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>330.72</t>
+          <t>2254670792367.41</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>328.35</t>
+          <t>2733957242169.27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>345.38</t>
+          <t>2973994348003.6</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>337.64</t>
+          <t>3277408780916.9</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>326.78</t>
+          <t>3649436127990.69</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>334.18</t>
+          <t>3835622783980.83</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>362.83</t>
+          <t>4450874913961.95</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>342.82</t>
+          <t>4419269411810.11</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>343.69</t>
+          <t>4192078800870.95</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>334.66</t>
+          <t>3960202373090.59</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>322.04</t>
+          <t>3487627740448.88</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>313.28</t>
+          <t>2787421875881.97</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>306.61</t>
+          <t>2222901542038.73</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>524.38</t>
+          <t>75260.6971182159</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>508.01</t>
+          <t>77186.7495395973</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>491.04</t>
+          <t>73026.5198838892</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>497.68</t>
+          <t>76640.2749238926</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>521.54</t>
+          <t>77362.0404008275</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>508.69</t>
+          <t>75856.154195472</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>496.49</t>
+          <t>78919.8362097961</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>504.41</t>
+          <t>82047.7350665363</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>383.68</t>
+          <t>101992.001705655</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>506.37</t>
+          <t>122693.660633994</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>509.12</t>
+          <t>133793.876633681</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>502.14</t>
+          <t>147182.496457625</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>525.34</t>
+          <t>174264.314043969</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>540.64</t>
+          <t>197448.313223165</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>533.1</t>
+          <t>153419.230800393</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12195030.857</t>
+          <t>2360395984836.84</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10757759.508</t>
+          <t>2173027968095.06</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>9987763.116</t>
+          <t>2138468147973.46</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>11512879.391</t>
+          <t>2520380327312.34</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>12414320.057</t>
+          <t>2745415279838.06</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>12912784.679</t>
+          <t>3016951721968.83</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13696114.984</t>
+          <t>3396664054370.75</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14226855.738</t>
+          <t>3392969998204.13</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>16623598.341</t>
+          <t>3993004020174.37</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>15701869.301</t>
+          <t>4000399160205.32</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>14626180.824</t>
+          <t>3852623031785.57</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>13327602.77</t>
+          <t>3598962738834.43</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>11464577.955</t>
+          <t>3125913407020.62</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>9790487.824</t>
+          <t>2566189194637.35</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>9064397.164</t>
+          <t>1991004138445.67</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10293939.797</t>
+          <t>-5039.50560782232</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8622738.4</t>
+          <t>-5557.3290236709</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7614459.545</t>
+          <t>-1820.97945440447</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8591732.047</t>
+          <t>502.847922446811</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>9352610.163</t>
+          <t>1399.50546521129</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9300852.285</t>
+          <t>2586.66857619994</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9551552.933</t>
+          <t>3359.73372325755</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>10012496.85</t>
+          <t>8487.06246392574</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>11938087.244</t>
+          <t>7350.60323042168</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>10740405.995</t>
+          <t>9358.27050856001</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>9968285.518</t>
+          <t>10511.9363175145</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>8834505.383</t>
+          <t>15454.7021096393</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>7419533.055</t>
+          <t>20423.7816495321</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>6137311.689</t>
+          <t>21129.8421853959</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5545137.538</t>
+          <t>14590.8770918695</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11358921.468</t>
+          <t>30880324202.4842</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9902551.878</t>
+          <t>3838429610.71873</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>9193773.489</t>
+          <t>116202644393.951</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10452005.637</t>
+          <t>213576914856.933</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>11068492.11</t>
+          <t>228579068165.534</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11425357.592</t>
+          <t>260457058948.076</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12247395.011</t>
+          <t>252772073619.944</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>12547991.834</t>
+          <t>442652785776.694</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>14639830.55</t>
+          <t>457870893787.58</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>13759707.891</t>
+          <t>418870251604.789</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>12699533.082</t>
+          <t>339455769085.376</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>11737173.649</t>
+          <t>361239634256.162</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>10082988.305</t>
+          <t>361714333428.255</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>7956110.61</t>
+          <t>221232681244.621</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>7197990.963</t>
+          <t>231897403593.055</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>104760.33174</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>101689.78559</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>89378.24209</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>91381.75096</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.463</t>
+          <t>90242.02239</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>81672.55084</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>80967.34353</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.457</t>
+          <t>86866.56089</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>106169.29782</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>120195.45537</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>122775.57934</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>131589.88057</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>153572.69415</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>167643.75389</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.796</t>
+          <t>150659.26576</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6758751.032</t>
+          <t>0.00608084257194367</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5873703.004</t>
+          <t>0.00579433175295169</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>5429940.045</t>
+          <t>0.00597893269181638</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6213616.616</t>
+          <t>0.0077520766430645</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6637622.876</t>
+          <t>0.00911292864216655</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6858667.583</t>
+          <t>0.0125526459412493</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>7229423.002</t>
+          <t>0.0151458364287322</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>7458640.763</t>
+          <t>0.0188882786259869</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>8652413.534</t>
+          <t>0.0200206636272875</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>8137240.539</t>
+          <t>0.0240893616746719</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>7435553.161</t>
+          <t>0.0272443225272672</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>6730609.556</t>
+          <t>0.0324683534033594</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5790322.408</t>
+          <t>0.0379579703162888</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4916017.896</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4573551.97</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>127992.186669422</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>123152.953138419</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>108742.303558698</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>111117.858937595</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>110147.54241072</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>98683.3827996589</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>97497.3858792404</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.272</t>
+          <t>104707.904963036</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>127950.733972506</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>143456.680272801</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>148695.16079702</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>157113.790745812</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>180261.99366911</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.522</t>
+          <t>204525.199765735</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>194288.149892041</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2296484.361</t>
+          <t>149675.606169677</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1982474.392</t>
+          <t>145738.318632223</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1797016.581</t>
+          <t>128695.957262441</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2038627.793</t>
+          <t>131521.983285444</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2151444.868</t>
+          <t>130408.256575546</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2182296.579</t>
+          <t>117186.843937276</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2303111.157</t>
+          <t>115641.130433391</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2380452.389</t>
+          <t>124600.275081746</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2760857.878</t>
+          <t>152362.597063906</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2558018.672</t>
+          <t>171096.132710131</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2358144.652</t>
+          <t>177805.570901088</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2132619.443</t>
+          <t>187820.15928529</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1831757.687</t>
+          <t>214640.180802592</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1553846.178</t>
+          <t>244328.853363102</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1434100.344</t>
+          <t>230988.738402635</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>858090.456761757</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>847096.229715934</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>762889.330515573</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>771212.170255622</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>752101.804375487</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>681310.690461719</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>676495.154287948</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>728771.629948285</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>888093.606229298</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>1000256.00286859</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>1027107.91024614</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>1071058.63251297</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>1216284.32354166</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1118.584</t>
+          <t>149675.606169677</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>995.415</t>
+          <t>152691.030601402</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1028.72</t>
+          <t>157461.764726779</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1155.691</t>
+          <t>162094.160196009</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1237.322</t>
+          <t>167394.104954669</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1383.042</t>
+          <t>170521.354659441</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1451.525</t>
+          <t>168774.187723964</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1374.48</t>
+          <t>170009.417192656</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1318.274</t>
+          <t>171811.297939903</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1070.374</t>
+          <t>174068.002670102</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>948.25</t>
+          <t>178699.732476272</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>796.084</t>
+          <t>183093.249167409</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>579.229</t>
+          <t>187721.335010179</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>394.906</t>
+          <t>196992.289731559</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>408.98</t>
+          <t>195767.940267466</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>127992.186669422</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>128756.933028637</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>133075.529494262</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>136679.262918424</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>141067.32458586</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>143759.007506718</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>142870.808695962</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>143608.416383328</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>144896.61670163</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>146330.37516427</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>149204.514366132</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>153538.354664414</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>158419.075301162</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>165301.617470886</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>164891.916656432</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>65118.9555803234</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>63864.1780177772</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>57432.6153275592</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>59556.7349545559</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>58757.9691744538</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>55145.1682927244</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>56348.2679366094</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>62333.5775582536</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>76159.4428560938</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>90060.0382798691</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>95170.4796889121</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>104115.87095471</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>122651.431407408</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>129268.073736898</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>112211.002247365</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>10293939796682.1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8622738400333.97</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>7614459544742.49</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8591732047484.02</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>9352610162870.8</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>9300852284665.88</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>9551552932521.1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>10012496849726.5</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>11938087243740.6</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>10740405994617.8</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>9968285517648.39</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>8834505382873.64</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>7419533054562.6</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6137311688509.41</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5545137538025.44</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>12195030856625.6</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>10757759508277</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>9987763115734.44</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>11512879391494.1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>12414320057144.5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>12912784678764.1</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>13696114984234.9</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>14226855738280.8</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>16623598340725.4</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>15701869301148.2</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>14626180823878.4</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>13327602769572.5</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>11464577954665.3</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>9790487824452.34</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>9064397164214.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>6758751031682.26</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5873703003740.59</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>5429940045287.89</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>6213616615876.72</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>6637622876075.15</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>6858667582734.06</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7229423001605.82</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>7458640762957.11</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>8652413533748.4</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>8137240539411.92</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>7435553161361.15</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>6730609556267.05</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5790322408114.74</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4916017896217.39</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4573551969964.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3717450</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3745607</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3773250</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3812808</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3880567</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3931132</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3958982</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>3959496</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>3971206</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>3986006</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4031292</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4090488</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4160866</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4300196.26714888</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4212848.58615411</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3126174</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3122592</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3150546</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3184499</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3238962</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3277641</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3300196</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>3292549</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>3301853</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3314964</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3352668</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3407542</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3479521</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3569279</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3543030</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6149242000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6212278000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>6288025000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6361278000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6424814000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>6518098000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6559398000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6542049000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6583091000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6630014000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6658907000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6717025000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>6788639000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6968039603.14124</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6613166129.92754</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>4827845000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4833915000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>4916552000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4991233000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>5053095000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5121332000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5161275000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5133780000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5169977000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5204784000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>5217574000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5277349000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>5371388000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>5486016000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>5327349000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.169044817094115</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.168630359599756</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.167903365965459</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.168023523377907</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.199963111373848</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.202676400790775</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.202802552594371</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.207401147367655</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.195924358814711</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.24918943413737</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.240157875391057</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.235950322844061</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.240306739208807</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.238106026799351</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.250441977970516</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.671010166280092</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.680511013366372</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.686200441353039</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.685156538978708</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.656510514138975</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.655278617902113</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.661846026462975</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.661078921494902</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.63577070785497</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.63137656510983</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.643327008916173</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.64238490261995</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.639442539353564</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.651407027183705</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.649049853514358</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.159945016625794</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.150858627033873</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.145896192681503</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.146819937643385</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.143526374487177</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.142044981307112</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.135351420942655</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.131519931137443</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.168304933330319</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.1194340007528</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.11651511569277</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.121664774535988</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.120250721437629</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.110486946016944</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.100508168515127</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.113137247731648</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.1130773975395</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.113718272828169</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.11418334035063</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.136361356854577</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.139704039706494</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.140254486022889</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.144158214523391</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.143225011137814</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.174623171220739</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.168877336334161</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.164995263524689</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.167797619169898</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.163870769885039</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.175496739843436</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.667441399753227</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.67965633652255</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.686852596963825</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.682352512144294</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.662085467053103</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.661808110937379</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.668640698699335</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.669477251930921</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.67036171385888</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.654647805504798</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.664638824404813</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.660742385300573</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.65102115522402</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.662419824639012</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.665221646858623</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.219421352515125</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.207266265937951</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.199429130208006</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.203464147505076</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.20155317609232</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.198487849356127</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.191104815277776</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.186364533545689</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.186413275003306</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.170729023274463</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.166483839261025</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.174262351174738</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.181181225606082</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.173709405475949</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.159281613297941</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>396167.78119</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>389425.34302</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>349702.38207</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>359863.73897</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>357693.89626</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>331113.21482</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>336888.92575</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>365545.88064</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>451468.87916</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>523577.54357</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>556508.18899</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>605744.10582</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>704248.97568</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>799375.40736</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>719449.87965</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>214794.56175</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>209602.49665</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>186128.57259</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>191078.71824</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>189166.22575</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>172332.01223</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>171989.39837</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>186933.85264</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>228522.03992</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>261156.17099</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>272976.05059</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>291936.03024</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>337291.61221</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>373596.9271</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>343199.74065</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>627966.047148864</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>643018.446992757</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>658133.880369315</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>674449.139747487</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>691479.658955472</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>710332.219848021</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>728424.579828148</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>742944.45226883</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>759153.168849483</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>774058.063538429</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>789134.284570129</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>806369.874104814</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>825345.996961871</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
